--- a/schemas/библиотека.xlsx
+++ b/schemas/библиотека.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="46">
   <si>
     <t xml:space="preserve">Table</t>
   </si>
@@ -52,6 +52,9 @@
     <t xml:space="preserve">References</t>
   </si>
   <si>
+    <t xml:space="preserve">ON DELETE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reader</t>
   </si>
   <si>
@@ -100,6 +103,9 @@
     <t xml:space="preserve">category(category_id)</t>
   </si>
   <si>
+    <t xml:space="preserve">SET NULL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Author</t>
   </si>
   <si>
@@ -110,6 +116,9 @@
   </si>
   <si>
     <t xml:space="preserve">book(book_id)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASCADE</t>
   </si>
   <si>
     <t xml:space="preserve">author(author_id)</t>
@@ -445,7 +454,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.11"/>
@@ -456,7 +465,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="3.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="23.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="22.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13.6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -490,148 +500,154 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -639,71 +655,77 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -711,76 +733,82 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -788,73 +816,79 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>36</v>
-      </c>
       <c r="F24" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
